--- a/정기/데이터 정리/하루 재화 정리 최종.xlsx
+++ b/정기/데이터 정리/하루 재화 정리 최종.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\데이터 정리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88A6D78-D384-4E4E-834A-D7D5EAA6358F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEC3120-99A6-4471-AC41-3199F0FC0957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40320" yWindow="0" windowWidth="23085" windowHeight="15480" activeTab="6" xr2:uid="{D2D37F6D-4275-4991-B10D-42AEDB9E4AB5}"/>
+    <workbookView xWindow="10440" yWindow="60" windowWidth="22830" windowHeight="15480" xr2:uid="{D2D37F6D-4275-4991-B10D-42AEDB9E4AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="계산" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -970,7 +970,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1022,6 +1022,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1140,7 +1146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1244,6 +1250,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1679,13 +1688,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="28">
-        <v>2.74</v>
+        <v>7.9</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="28">
-        <v>2.38</v>
+        <v>7.9</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1732,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="27">
-        <v>828</v>
+        <v>655</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1785,26 +1794,26 @@
       </c>
       <c r="B4" s="4" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">INDIRECT("오프라인보상!"&amp;CHAR(COLUMN(A3)+64)&amp;($B3+1))</f>
-        <v>543941</v>
+        <v>429025</v>
       </c>
       <c r="C4" s="4" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDIRECT("오프라인보상!"&amp;CHAR(COLUMN(B3)+64)&amp;($B3+1))</f>
-        <v>410</v>
+        <v>325</v>
       </c>
       <c r="D4" s="4" cm="1">
-        <f t="array" aca="1" ref="D4" ca="1">INDIRECT("오프라인보상!"&amp;CHAR(COLUMN(C3)+64)&amp;($B3+1))</f>
-        <v>1213</v>
+        <f t="array" aca="1" ref="D4" ca="1">INDIRECT("오프라인보상!D" &amp; B3)</f>
+        <v>0</v>
       </c>
       <c r="E4" s="4" cm="1">
-        <f t="array" aca="1" ref="E4" ca="1">INDIRECT("오프라인보상!"&amp;CHAR(COLUMN(B2)+64)&amp;($B3+1))</f>
-        <v>410</v>
+        <f t="array" aca="1" ref="E4" ca="1">INDIRECT("오프라인보상!G" &amp; B3)</f>
+        <v>14</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="4" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDIRECT("오프라인보상!"&amp;CHAR(COLUMN(F3)+64)&amp;($B3+1))</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H4" s="4" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">INDIRECT("오프라인보상!"&amp;CHAR(COLUMN(G3)+64)&amp;($B3+1))</f>
@@ -1911,19 +1920,19 @@
       </c>
       <c r="B7" s="11">
         <f ca="1">B4*12*60*C2</f>
-        <v>1073086804.8000001</v>
+        <v>2440294200</v>
       </c>
       <c r="C7" s="10">
-        <f ca="1">C4*12*60*E2</f>
-        <v>702576</v>
+        <f ca="1">C4*12*60*C2</f>
+        <v>1848600</v>
       </c>
       <c r="D7" s="10">
         <f ca="1">E4*12*60</f>
-        <v>295200</v>
+        <v>10080</v>
       </c>
       <c r="E7" s="10">
-        <f ca="1">H4*12*60</f>
-        <v>10080</v>
+        <f ca="1">E4*12*60*E2</f>
+        <v>79632</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="15" t="s">
@@ -3920,7 +3929,7 @@
       </c>
       <c r="B45" s="20">
         <f ca="1">B4*25*L49</f>
-        <v>73820564.285714284</v>
+        <v>58224821.428571433</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
@@ -3932,11 +3941,11 @@
       </c>
       <c r="H45" s="15">
         <f>1.5*10*B3*P49</f>
-        <v>727457.14285714284</v>
+        <v>575464.28571428568</v>
       </c>
       <c r="I45" s="15">
         <f>1.5*10*B3*P49</f>
-        <v>727457.14285714284</v>
+        <v>575464.28571428568</v>
       </c>
       <c r="J45" s="15"/>
       <c r="K45" s="15"/>
@@ -4125,19 +4134,19 @@
     <row r="49" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B49" s="3">
         <f t="shared" ref="B49:P49" ca="1" si="1">SUM(B7:B47)</f>
-        <v>1146907369.0857143</v>
+        <v>2498519021.4285712</v>
       </c>
       <c r="C49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>992321.71428571432</v>
+        <v>2138345.7142857146</v>
       </c>
       <c r="D49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1382748</v>
+        <v>1097628</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>87819.160095238112</v>
+        <v>157371.1600952381</v>
       </c>
       <c r="F49" s="3">
         <f t="shared" si="1"/>
@@ -4149,11 +4158,11 @@
       </c>
       <c r="H49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>738977.14285714284</v>
+        <v>586984.28571428568</v>
       </c>
       <c r="I49" s="3">
         <f t="shared" si="1"/>
-        <v>727457.14285714284</v>
+        <v>575464.28571428568</v>
       </c>
       <c r="J49" s="3">
         <f t="shared" si="1"/>
@@ -4241,7 +4250,7 @@
       </c>
       <c r="E51" s="22">
         <f ca="1">SUM(E49:E50)</f>
-        <v>57819.160095238112</v>
+        <v>127371.1600952381</v>
       </c>
       <c r="AB51">
         <v>52</v>
@@ -7918,6 +7927,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B6D15A-ADDB-49F6-99A2-892989D6F6FC}">
   <dimension ref="A1:I1501"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -23986,31 +23998,31 @@
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A555">
+      <c r="A555" s="35">
         <v>306916</v>
       </c>
-      <c r="B555">
+      <c r="B555" s="35">
         <v>275</v>
       </c>
-      <c r="C555">
+      <c r="C555" s="35">
         <v>802</v>
       </c>
-      <c r="D555">
-        <v>0</v>
-      </c>
-      <c r="E555">
-        <v>17</v>
-      </c>
-      <c r="F555">
+      <c r="D555" s="35">
+        <v>0</v>
+      </c>
+      <c r="E555" s="35">
+        <v>17</v>
+      </c>
+      <c r="F555" s="35">
         <v>0.05</v>
       </c>
-      <c r="G555">
-        <v>14</v>
-      </c>
-      <c r="H555">
-        <v>16</v>
-      </c>
-      <c r="I555">
+      <c r="G555" s="35">
+        <v>14</v>
+      </c>
+      <c r="H555" s="35">
+        <v>16</v>
+      </c>
+      <c r="I555" s="35">
         <v>0</v>
       </c>
     </row>
@@ -51805,18 +51817,18 @@
       <c r="L1" t="s">
         <v>130</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="N1" s="35"/>
+      <c r="N1" s="36"/>
       <c r="O1" t="s">
         <v>132</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
       <c r="V1" t="s">
         <v>134</v>
       </c>

--- a/정기/데이터 정리/하루 재화 정리 최종.xlsx
+++ b/정기/데이터 정리/하루 재화 정리 최종.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\데이터 정리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEC3120-99A6-4471-AC41-3199F0FC0957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A9647C-22CA-4B09-B77E-3F6125C00226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="60" windowWidth="22830" windowHeight="15480" xr2:uid="{D2D37F6D-4275-4991-B10D-42AEDB9E4AB5}"/>
+    <workbookView xWindow="12015" yWindow="135" windowWidth="19200" windowHeight="15480" xr2:uid="{D2D37F6D-4275-4991-B10D-42AEDB9E4AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="계산" sheetId="1" r:id="rId1"/>
     <sheet name="오프라인보상" sheetId="2" r:id="rId2"/>
     <sheet name="기존 재화 가치" sheetId="5" r:id="rId3"/>
     <sheet name="유저 일일 분석" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId5"/>
-    <sheet name="통계" sheetId="6" r:id="rId6"/>
-    <sheet name="소환" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="206">
   <si>
     <t>스테이지</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -856,60 +853,6 @@
     <t>끔</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
-  <si>
-    <t>순번</t>
-  </si>
-  <si>
-    <t>값</t>
-  </si>
-  <si>
-    <t>100만 다이아 레벨5상자로 다 뽑음</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>7레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고려</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>평균조각</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>9이찰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>현질 1~3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이아(천만)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>조선</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>총조각수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -920,7 +863,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -957,15 +900,6 @@
       <color theme="4" tint="-0.249977111117893"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -1146,7 +1080,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1238,18 +1172,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
@@ -23998,31 +23920,31 @@
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A555" s="35">
+      <c r="A555" s="31">
         <v>306916</v>
       </c>
-      <c r="B555" s="35">
+      <c r="B555" s="31">
         <v>275</v>
       </c>
-      <c r="C555" s="35">
+      <c r="C555" s="31">
         <v>802</v>
       </c>
-      <c r="D555" s="35">
-        <v>0</v>
-      </c>
-      <c r="E555" s="35">
-        <v>17</v>
-      </c>
-      <c r="F555" s="35">
+      <c r="D555" s="31">
+        <v>0</v>
+      </c>
+      <c r="E555" s="31">
+        <v>17</v>
+      </c>
+      <c r="F555" s="31">
         <v>0.05</v>
       </c>
-      <c r="G555" s="35">
-        <v>14</v>
-      </c>
-      <c r="H555" s="35">
-        <v>16</v>
-      </c>
-      <c r="I555" s="35">
+      <c r="G555" s="31">
+        <v>14</v>
+      </c>
+      <c r="H555" s="31">
+        <v>16</v>
+      </c>
+      <c r="I555" s="31">
         <v>0</v>
       </c>
     </row>
@@ -51817,18 +51739,18 @@
       <c r="L1" t="s">
         <v>130</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="M1" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="N1" s="36"/>
+      <c r="N1" s="32"/>
       <c r="O1" t="s">
         <v>132</v>
       </c>
-      <c r="S1" s="36" t="s">
+      <c r="S1" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
       <c r="V1" t="s">
         <v>134</v>
       </c>
@@ -52397,626 +52319,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E82EBAC8-3689-4579-883C-82D442363E10}">
-  <dimension ref="D5:E6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E6">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887CF9C8-EF0A-43A4-91A3-BE8124351CBB}">
-  <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="32">
-        <v>1</v>
-      </c>
-      <c r="B2" s="32">
-        <v>1667</v>
-      </c>
-      <c r="F2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="32">
-        <v>2</v>
-      </c>
-      <c r="B3" s="32">
-        <v>1597</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>63.335000000000001</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <f>G3*F3/100</f>
-        <v>0.63334999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="32">
-        <v>3</v>
-      </c>
-      <c r="B4" s="32">
-        <v>1578</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>26.47</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H8" si="0">G4*F4/100</f>
-        <v>1.0588</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="32">
-        <v>4</v>
-      </c>
-      <c r="B5" s="32">
-        <v>1528</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="32">
-        <v>5</v>
-      </c>
-      <c r="B6" s="32">
-        <v>1423</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>64</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="32">
-        <v>6</v>
-      </c>
-      <c r="B7" s="32">
-        <v>1401</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>0.17</v>
-      </c>
-      <c r="G7">
-        <v>256</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>0.43520000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="32">
-        <v>7</v>
-      </c>
-      <c r="B8" s="32">
-        <v>1339</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="G8">
-        <v>1024</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>0.25600000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="32">
-        <v>8</v>
-      </c>
-      <c r="B9" s="32">
-        <v>1298</v>
-      </c>
-      <c r="F9">
-        <f>SUM(F3:F8)</f>
-        <v>100.00000000000001</v>
-      </c>
-      <c r="H9" s="33">
-        <f>SUM(H3:H8)</f>
-        <v>4.4633500000000002</v>
-      </c>
-      <c r="I9">
-        <v>150</v>
-      </c>
-      <c r="J9" s="3">
-        <v>10000000</v>
-      </c>
-      <c r="K9">
-        <f>J9/I9*H9</f>
-        <v>297556.66666666669</v>
-      </c>
-      <c r="L9">
-        <f>K9/18</f>
-        <v>16530.925925925927</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="32">
-        <v>9</v>
-      </c>
-      <c r="B10" s="32">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="32">
-        <v>10</v>
-      </c>
-      <c r="B11" s="32">
-        <v>1279</v>
-      </c>
-      <c r="F11" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="32">
-        <v>11</v>
-      </c>
-      <c r="B12" s="32">
-        <v>1277</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>66.778000000000006</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <f>G12*F12/100</f>
-        <v>0.66778000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="32">
-        <v>12</v>
-      </c>
-      <c r="B13" s="32">
-        <v>1145</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>24.15</v>
-      </c>
-      <c r="G13">
-        <v>4</v>
-      </c>
-      <c r="H13">
-        <f t="shared" ref="H13:H17" si="1">G13*F13/100</f>
-        <v>0.96599999999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="32">
-        <v>13</v>
-      </c>
-      <c r="B14" s="32">
-        <v>1143</v>
-      </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <v>8</v>
-      </c>
-      <c r="G14">
-        <v>16</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="1"/>
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="32">
-        <v>14</v>
-      </c>
-      <c r="B15" s="32">
-        <v>1118</v>
-      </c>
-      <c r="E15">
-        <v>4</v>
-      </c>
-      <c r="F15">
-        <v>0.9</v>
-      </c>
-      <c r="G15">
-        <v>64</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>0.57600000000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="32">
-        <v>15</v>
-      </c>
-      <c r="B16" s="32">
-        <v>1096</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16">
-        <v>0.15</v>
-      </c>
-      <c r="G16">
-        <v>256</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>0.38400000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="32">
-        <v>16</v>
-      </c>
-      <c r="B17" s="32">
-        <v>1095</v>
-      </c>
-      <c r="E17">
-        <v>6</v>
-      </c>
-      <c r="F17">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G17">
-        <v>1024</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>0.22527999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="32">
-        <v>17</v>
-      </c>
-      <c r="B18" s="32">
-        <v>1074</v>
-      </c>
-      <c r="H18" s="33">
-        <f>SUM(H12:H17)</f>
-        <v>4.0990599999999997</v>
-      </c>
-      <c r="I18">
-        <v>150</v>
-      </c>
-      <c r="J18">
-        <v>1000000</v>
-      </c>
-      <c r="K18">
-        <f>J18/I18*H18</f>
-        <v>27327.066666666666</v>
-      </c>
-      <c r="L18">
-        <f>K18/18</f>
-        <v>1518.1703703703704</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="32">
-        <v>18</v>
-      </c>
-      <c r="B19" s="32">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="32">
-        <v>19</v>
-      </c>
-      <c r="B20" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F21" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>208</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>70.221000000000004</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <f>G22*F22/100</f>
-        <v>0.70221</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>21.83</v>
-      </c>
-      <c r="G23">
-        <v>4</v>
-      </c>
-      <c r="H23">
-        <f t="shared" ref="H23:H27" si="2">G23*F23/100</f>
-        <v>0.87319999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>59</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24">
-        <f>B24*A24</f>
-        <v>236</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
-      <c r="F24">
-        <v>7</v>
-      </c>
-      <c r="G24">
-        <v>16</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="2"/>
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25">
-        <v>0.8</v>
-      </c>
-      <c r="G25">
-        <v>64</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="2"/>
-        <v>0.51200000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E26">
-        <v>5</v>
-      </c>
-      <c r="F26">
-        <v>0.13</v>
-      </c>
-      <c r="G26">
-        <v>256</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="2"/>
-        <v>0.33279999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E27">
-        <v>6</v>
-      </c>
-      <c r="F27">
-        <v>1.9E-2</v>
-      </c>
-      <c r="G27">
-        <v>1024</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="2"/>
-        <v>0.19455999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H28" s="33">
-        <f>SUM(H22:H27)</f>
-        <v>3.7347700000000001</v>
-      </c>
-      <c r="I28">
-        <v>150</v>
-      </c>
-      <c r="J28">
-        <v>1000000</v>
-      </c>
-      <c r="K28">
-        <f>J28/I28*H28</f>
-        <v>24898.466666666667</v>
-      </c>
-      <c r="L28">
-        <f>K28/18</f>
-        <v>1383.2481481481482</v>
-      </c>
-    </row>
-    <row r="35" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="F35">
-        <v>500</v>
-      </c>
-      <c r="G35">
-        <v>25</v>
-      </c>
-      <c r="H35">
-        <f>F35/G35</f>
-        <v>20</v>
-      </c>
-      <c r="I35">
-        <f>H35*5.9</f>
-        <v>118</v>
-      </c>
-      <c r="K35">
-        <f>I35/18</f>
-        <v>6.5555555555555554</v>
-      </c>
-      <c r="M35">
-        <f>K35*5.9</f>
-        <v>38.677777777777777</v>
-      </c>
-    </row>
-    <row r="36" spans="6:13" x14ac:dyDescent="0.3">
-      <c r="K36">
-        <f>K35*4</f>
-        <v>26.222222222222221</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D7AE86-EF06-476F-A308-7B8157BFE0D9}">
-  <dimension ref="D1:H3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="E1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G1" t="s">
-        <v>218</v>
-      </c>
-      <c r="H1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2">
-        <v>10000000</v>
-      </c>
-      <c r="F2" s="34">
-        <v>16968.669999999998</v>
-      </c>
-      <c r="G2">
-        <v>29000</v>
-      </c>
-      <c r="H2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E3">
-        <v>10000000</v>
-      </c>
-      <c r="F3">
-        <v>12000</v>
-      </c>
-      <c r="G3">
-        <v>28000</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>